--- a/isms-core-framework/A.6-people-controls/isms-a.6.7-8-remote-working-and-reporting/WKBK/ISMS-IMP-A.6.7-8.S1_Remote_Work_Authorisation_Assessment_20260301.xlsx
+++ b/isms-core-framework/A.6-people-controls/isms-a.6.7-8-remote-working-and-reporting/WKBK/ISMS-IMP-A.6.7-8.S1_Remote_Work_Authorisation_Assessment_20260301.xlsx
@@ -28,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,22 +105,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00003366"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="15">
@@ -202,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -216,39 +200,11 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -339,22 +295,17 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -984,14 +935,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -1019,7 +970,7 @@
     <row r="3">
       <c r="A3" s="41" t="inlineStr">
         <is>
-          <t>ASSESSMENT REVIEW AND APPROVAL</t>
+          <t>ASSESSMENT SUMMARY</t>
         </is>
       </c>
       <c r="B3" s="6" t="n"/>
@@ -1030,141 +981,357 @@
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
         <is>
-          <t>Role / Function</t>
-        </is>
-      </c>
-      <c r="B4" s="42" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C4" s="42" t="inlineStr">
-        <is>
-          <t>Signature / Initials</t>
-        </is>
-      </c>
-      <c r="D4" s="42" t="inlineStr">
-        <is>
-          <t>Date (DD.MM.YYYY)</t>
-        </is>
-      </c>
-      <c r="E4" s="42" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
+          <t>Document:</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>ISMS-IMP-A.6.7-8.S1 - Remote Work Authorisation Assessment</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
-        <is>
-          <t>Lead Assessor / Author</t>
-        </is>
-      </c>
-      <c r="B5" s="44" t="inlineStr"/>
-      <c r="C5" s="44" t="inlineStr"/>
-      <c r="D5" s="44" t="inlineStr"/>
-      <c r="E5" s="44" t="inlineStr"/>
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>Assessment Period:</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
-        <is>
-          <t>IT Security Manager</t>
-        </is>
-      </c>
-      <c r="B6" s="44" t="inlineStr"/>
-      <c r="C6" s="44" t="inlineStr"/>
-      <c r="D6" s="44" t="inlineStr"/>
-      <c r="E6" s="44" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="inlineStr">
-        <is>
-          <t>Reviewer (Technical / Compliance)</t>
-        </is>
-      </c>
-      <c r="B7" s="44" t="inlineStr"/>
-      <c r="C7" s="44" t="inlineStr"/>
-      <c r="D7" s="44" t="inlineStr"/>
-      <c r="E7" s="44" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="inlineStr">
-        <is>
-          <t>CISO / Final Approver</t>
-        </is>
-      </c>
-      <c r="B8" s="44" t="inlineStr"/>
-      <c r="C8" s="44" t="inlineStr"/>
-      <c r="D8" s="44" t="inlineStr"/>
-      <c r="E8" s="44" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="45" t="inlineStr">
-        <is>
-          <t>FINAL DECISION:</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="41" t="inlineStr">
-        <is>
-          <t>NEXT REVIEW</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="46" t="inlineStr">
-        <is>
-          <t>Next Review Date:</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="46" t="inlineStr">
-        <is>
-          <t>Review Trigger / Notes:</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="46" t="inlineStr">
-        <is>
-          <t>Overall Compliance %:</t>
-        </is>
-      </c>
-      <c r="B16" s="47">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>Overall Compliance Rating:</t>
+        </is>
+      </c>
+      <c r="B6" s="43">
         <f>IFERROR(AVERAGE('Summary Dashboard'!G6:G10),"")</f>
         <v/>
       </c>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>Assessment Status:</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>Assessed By:</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>COMPLETED BY (ASSESSOR)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>Name:</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>Title:</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>Date:</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>Signature:</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="41" t="inlineStr">
+        <is>
+          <t>REVIEWED BY (INFORMATION SECURITY OFFICER)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>Name:</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>Title:</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>Date:</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>Signature:</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>APPROVED BY (CISO)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t>Name:</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>Title:</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>Date:</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="42" t="inlineStr">
+        <is>
+          <t>Signature:</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="42" t="inlineStr">
+        <is>
+          <t>FINAL DECISION:</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>NEXT REVIEW DETAILS</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>Next Review Date:</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="42" t="inlineStr">
+        <is>
+          <t>Review Responsible:</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="42" t="inlineStr">
+        <is>
+          <t>Special Considerations:</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="31">
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B27:E27"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="B8:E8"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B28:E28"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Draft,Final,Requires remediation,Re-assessment required"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approved,Approved with Conditions,Rejected,Deferred"</formula1>
     </dataValidation>
   </dataValidations>
